--- a/Data/Hires/testDataIreland.xlsx
+++ b/Data/Hires/testDataIreland.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3E79D2-F9EE-4C5C-BE9D-D967A5EFEC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E937B691-ADD3-4F14-B487-E1C74E34A632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -213,10 +213,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Joannie</t>
-  </si>
-  <si>
-    <t>Spinka</t>
+    <t>Moises</t>
+  </si>
+  <si>
+    <t>Gutkowski</t>
   </si>
   <si>
     <t>Landline</t>
@@ -285,6 +285,9 @@
     <t>Personal Public Service Number (PPS no)</t>
   </si>
   <si>
+    <t>1234732TW</t>
+  </si>
+  <si>
     <t>Male</t>
   </si>
   <si>
@@ -327,13 +330,13 @@
     <t>001 Store Management (Savip Gytape (100446))</t>
   </si>
   <si>
-    <t>Ollie</t>
-  </si>
-  <si>
-    <t>Moen</t>
-  </si>
-  <si>
-    <t>Auto 59907084</t>
+    <t>Abdul</t>
+  </si>
+  <si>
+    <t>Gerhold</t>
+  </si>
+  <si>
+    <t>Auto 28682915</t>
   </si>
   <si>
     <t>Department Manager</t>
@@ -342,13 +345,10 @@
     <t>92 Retail Management</t>
   </si>
   <si>
-    <t>1234728TW</t>
+    <t>1234733TW</t>
   </si>
   <si>
     <t>IE Management Group 20</t>
-  </si>
-  <si>
-    <t>1234730TW</t>
   </si>
 </sst>
 </file>
@@ -455,7 +455,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -536,7 +536,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -569,9 +569,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -625,7 +623,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1147,11 +1144,11 @@
       <c r="A2" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="12">
-        <v>10699554</v>
-      </c>
-      <c r="C2" s="32" t="s">
-        <v>97</v>
+      <c r="B2" s="31">
+        <v>10699610</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>98</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>58</v>
@@ -1179,7 +1176,7 @@
       </c>
       <c r="L2" s="18">
         <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45782</v>
+        <v>45788</v>
       </c>
       <c r="M2" s="14" t="s">
         <v>65</v>
@@ -1216,11 +1213,11 @@
       </c>
       <c r="X2" s="22">
         <f t="shared" ref="X2:X3" ca="1" si="1">L2</f>
-        <v>45782</v>
+        <v>45788</v>
       </c>
       <c r="Y2" s="18">
         <f t="shared" ref="Y2:Y3" ca="1" si="2">X2+90</f>
-        <v>45872</v>
+        <v>45878</v>
       </c>
       <c r="Z2" s="17" t="s">
         <v>71</v>
@@ -1277,10 +1274,10 @@
         <v>84</v>
       </c>
       <c r="AR2" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="AS2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AT2" s="29">
         <v>35591</v>
@@ -1295,51 +1292,51 @@
         <v>66</v>
       </c>
       <c r="AX2" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY2" s="29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AZ2" s="29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="BA2" s="29" t="s">
         <v>65</v>
       </c>
       <c r="BB2" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="BC2" s="28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="BD2" s="28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BE2" s="28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="BF2" s="28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="BG2" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BH2" s="30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B3" s="31">
-        <v>10699540</v>
-      </c>
-      <c r="C3" s="32" t="s">
-        <v>97</v>
+        <v>10699611</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>98</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>59</v>
@@ -1348,10 +1345,10 @@
         <v>60</v>
       </c>
       <c r="G3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I3" s="17">
         <v>861240232</v>
@@ -1364,7 +1361,7 @@
       </c>
       <c r="L3" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>45782</v>
+        <v>45788</v>
       </c>
       <c r="M3" s="14" t="s">
         <v>65</v>
@@ -1401,23 +1398,23 @@
       </c>
       <c r="X3" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>45782</v>
+        <v>45788</v>
       </c>
       <c r="Y3" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>45872</v>
+        <v>45878</v>
       </c>
       <c r="Z3" s="17" t="s">
         <v>71</v>
       </c>
       <c r="AA3" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AB3" s="24" t="s">
         <v>73</v>
       </c>
       <c r="AC3" s="25" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AD3" s="24" t="s">
         <v>75</v>
@@ -1444,9 +1441,9 @@
         <v>81</v>
       </c>
       <c r="AL3" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="AM3" s="33">
+        <v>104</v>
+      </c>
+      <c r="AM3" s="32">
         <v>251</v>
       </c>
       <c r="AN3" s="27" t="s">
@@ -1462,10 +1459,10 @@
         <v>84</v>
       </c>
       <c r="AR3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AS3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AT3" s="29">
         <v>35591</v>
@@ -1480,37 +1477,37 @@
         <v>66</v>
       </c>
       <c r="AX3" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY3" s="29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AZ3" s="29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="BA3" s="29" t="s">
         <v>65</v>
       </c>
       <c r="BB3" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="BC3" s="28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="BD3" s="28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BE3" s="28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="BF3" s="28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="BG3" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BH3" s="30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1524,6 +1521,6 @@
     <hyperlink ref="V3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId3"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/Hires/testDataIreland.xlsx
+++ b/Data/Hires/testDataIreland.xlsx
@@ -1,34 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E937B691-ADD3-4F14-B487-E1C74E34A632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="109">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -204,6 +190,12 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t>10699741</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>001 Recruitment (Lubym Wyvyfu (221849))</t>
   </si>
   <si>
@@ -213,10 +205,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Moises</t>
-  </si>
-  <si>
-    <t>Gutkowski</t>
+    <t>Jayda</t>
+  </si>
+  <si>
+    <t>Lakin</t>
   </si>
   <si>
     <t>Landline</t>
@@ -285,7 +277,7 @@
     <t>Personal Public Service Number (PPS no)</t>
   </si>
   <si>
-    <t>1234732TW</t>
+    <t>1234735TW</t>
   </si>
   <si>
     <t>Male</t>
@@ -324,19 +316,19 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>Passed</t>
+    <t>10699757</t>
   </si>
   <si>
     <t>001 Store Management (Savip Gytape (100446))</t>
   </si>
   <si>
-    <t>Abdul</t>
-  </si>
-  <si>
-    <t>Gerhold</t>
-  </si>
-  <si>
-    <t>Auto 28682915</t>
+    <t>Mandy</t>
+  </si>
+  <si>
+    <t>Raynor</t>
+  </si>
+  <si>
+    <t>Auto 16592845</t>
   </si>
   <si>
     <t>Department Manager</t>
@@ -345,7 +337,7 @@
     <t>92 Retail Management</t>
   </si>
   <si>
-    <t>1234733TW</t>
+    <t>1234738TW</t>
   </si>
   <si>
     <t>IE Management Group 20</t>
@@ -354,66 +346,66 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="9" tint="-0.249977111117893"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="9" tint="-0.249977111117893"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FF4A4A4A"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -431,19 +423,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -469,25 +461,15 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
@@ -498,27 +480,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -569,6 +539,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -620,9 +593,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -905,9 +875,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BH3"/>
-  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23.6328125" customWidth="1"/>
     <col min="2" max="2" width="68.08984375" customWidth="1"/>
@@ -958,7 +928,7 @@
     <col min="100" max="100" width="34.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="51" customHeight="1" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1140,387 +1110,402 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:60" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="87.5" customHeight="1" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="31">
-        <v>10699610</v>
-      </c>
-      <c r="C2" s="12" t="s">
+      <c r="B2" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" s="18">
+        <v>861240232</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="L2" s="19">
+        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
+        <v>45795</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N2" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="O2" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="P2" s="18">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="R2" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="S2" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="T2" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="U2" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="V2" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="W2" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2" s="23">
+        <f t="shared" ref="X2:X3" si="1">L2</f>
+        <v>45795</v>
+      </c>
+      <c r="Y2" s="19">
+        <f t="shared" ref="Y2:Y3" si="2">X2+90</f>
+        <v>45885</v>
+      </c>
+      <c r="Z2" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA2" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB2" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC2" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD2" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE2" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF2" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG2" s="27">
+        <v>37.5</v>
+      </c>
+      <c r="AH2" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ2" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK2" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL2" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN2" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO2" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP2" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ2" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT2" s="30">
+        <v>35591</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW2" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="AX2" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="AY2" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AZ2" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="BA2" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB2" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC2" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="BD2" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="BE2" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="BF2" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="BG2" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="BH2" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="14" t="s">
+    </row>
+    <row r="3" ht="14.5" customHeight="1" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G2" s="16" t="s">
+      <c r="D3" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="F3" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="I2" s="17">
+      <c r="G3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I3" s="18">
         <v>861240232</v>
       </c>
-      <c r="J2" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="L2" s="18">
-        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45788</v>
-      </c>
-      <c r="M2" s="14" t="s">
+      <c r="J3" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="K3" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="L3" s="19">
+        <f t="shared" si="0"/>
+        <v>45795</v>
+      </c>
+      <c r="M3" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="P2" s="17">
+      <c r="N3" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="O3" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="P3" s="18">
         <v>38</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="Q3" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="R3" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="S3" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="T3" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="R2" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="S2" s="17" t="s">
+      <c r="U3" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="V3" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="W3" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="T2" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="U2" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="V2" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="W2" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="X2" s="22">
-        <f t="shared" ref="X2:X3" ca="1" si="1">L2</f>
-        <v>45788</v>
-      </c>
-      <c r="Y2" s="18">
-        <f t="shared" ref="Y2:Y3" ca="1" si="2">X2+90</f>
-        <v>45878</v>
-      </c>
-      <c r="Z2" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA2" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB2" s="24" t="s">
+      <c r="X3" s="23">
+        <f t="shared" si="1"/>
+        <v>45795</v>
+      </c>
+      <c r="Y3" s="19">
+        <f t="shared" si="2"/>
+        <v>45885</v>
+      </c>
+      <c r="Z3" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="AC2" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD2" s="24" t="s">
+      <c r="AA3" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB3" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="AE2" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF2" s="14" t="s">
+      <c r="AC3" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="AD3" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AG2" s="26">
+      <c r="AE3" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF3" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG3" s="27">
         <v>37.5</v>
       </c>
-      <c r="AH2" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ2" s="22" t="s">
+      <c r="AH3" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="AK2" s="17" t="s">
+      <c r="AI3" t="s">
         <v>81</v>
       </c>
-      <c r="AL2" s="17" t="s">
+      <c r="AJ3" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AK3" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="AN2" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="AO2" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="AP2" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="AQ2" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AT2" s="29">
-        <v>35591</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AW2" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX2" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="AY2" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="AZ2" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="BA2" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="BB2" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="BC2" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="BD2" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="BE2" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="BF2" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="BG2" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="BH2" s="30" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3" s="31">
-        <v>10699611</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G3" t="s">
-        <v>100</v>
-      </c>
-      <c r="H3" t="s">
-        <v>101</v>
-      </c>
-      <c r="I3" s="17">
-        <v>861240232</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="L3" s="18">
-        <f t="shared" ca="1" si="0"/>
-        <v>45788</v>
-      </c>
-      <c r="M3" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="N3" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="O3" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="P3" s="17">
-        <v>38</v>
-      </c>
-      <c r="Q3" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="R3" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="S3" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="T3" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="U3" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="V3" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="W3" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="X3" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>45788</v>
-      </c>
-      <c r="Y3" s="18">
-        <f t="shared" ca="1" si="2"/>
-        <v>45878</v>
-      </c>
-      <c r="Z3" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA3" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="AB3" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC3" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="AD3" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE3" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF3" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG3" s="26">
-        <v>37.5</v>
-      </c>
-      <c r="AH3" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ3" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK3" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL3" s="17" t="s">
-        <v>104</v>
+      <c r="AL3" s="18" t="s">
+        <v>106</v>
       </c>
       <c r="AM3" s="32">
         <v>251</v>
       </c>
-      <c r="AN3" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="AO3" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="AP3" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="AQ3" s="28" t="s">
-        <v>84</v>
+      <c r="AN3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP3" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ3" s="29" t="s">
+        <v>86</v>
       </c>
       <c r="AR3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AS3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AT3" s="29">
+        <v>88</v>
+      </c>
+      <c r="AT3" s="30">
         <v>35591</v>
       </c>
       <c r="AU3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AV3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AW3" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX3" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="AY3" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="AZ3" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW3" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="AX3" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="BA3" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="BB3" s="14" t="s">
+      <c r="AY3" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="BC3" s="28" t="s">
+      <c r="AZ3" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="BD3" s="28" t="s">
+      <c r="BA3" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB3" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="BE3" s="28" t="s">
+      <c r="BC3" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="BF3" s="28" t="s">
+      <c r="BD3" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="BG3" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="BH3" s="30" t="s">
+      <c r="BE3" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="BF3" s="29" t="s">
         <v>96</v>
+      </c>
+      <c r="BG3" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="BH3" s="31" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX3 Z2:Z3 W2:W3 T2:T3 K2:K3 BF2:BF3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z3">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="V3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="V2" r:id="rId1"/>
+    <hyperlink ref="V3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/Hires/testDataIreland.xlsx
+++ b/Data/Hires/testDataIreland.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F432E808-846C-44B9-9CC0-E8429FF8E986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99EFB12A-BED2-453A-97A7-CA074F05E1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -213,10 +213,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Tiana</t>
-  </si>
-  <si>
-    <t>Huel-Crist</t>
+    <t>Alfredo</t>
+  </si>
+  <si>
+    <t>Gibson</t>
   </si>
   <si>
     <t>Landline</t>
@@ -285,7 +285,7 @@
     <t>Personal Public Service Number (PPS no)</t>
   </si>
   <si>
-    <t>1234748TW</t>
+    <t>1234758TW</t>
   </si>
   <si>
     <t>Male</t>
@@ -327,13 +327,13 @@
     <t>001 Store Management (Savip Gytape (100446))</t>
   </si>
   <si>
-    <t>Alec</t>
-  </si>
-  <si>
-    <t>Wisozk</t>
-  </si>
-  <si>
-    <t>Auto 21279645</t>
+    <t>Madyson</t>
+  </si>
+  <si>
+    <t>Durgan</t>
+  </si>
+  <si>
+    <t>Auto 34006623</t>
   </si>
   <si>
     <t>Department Manager</t>
@@ -342,7 +342,7 @@
     <t>92 Retail Management</t>
   </si>
   <si>
-    <t>1234749TW</t>
+    <t>1234759TW</t>
   </si>
   <si>
     <t>IE Management Group 20</t>
@@ -387,6 +387,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="9" tint="-0.249977111117893"/>
       <name val="Calibri"/>
@@ -411,14 +419,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -545,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -578,10 +578,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -602,7 +602,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -613,7 +613,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
@@ -630,11 +630,10 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1154,9 +1153,9 @@
         <v>57</v>
       </c>
       <c r="B2" s="12">
-        <v>10700246</v>
-      </c>
-      <c r="C2" s="32" t="s">
+        <v>10700451</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>106</v>
       </c>
       <c r="D2" s="13" t="s">
@@ -1185,7 +1184,7 @@
       </c>
       <c r="L2" s="18">
         <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="M2" s="14" t="s">
         <v>65</v>
@@ -1222,11 +1221,11 @@
       </c>
       <c r="X2" s="22">
         <f t="shared" ref="X2:X3" ca="1" si="1">L2</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="Y2" s="18">
         <f t="shared" ref="Y2:Y3" ca="1" si="2">X2+90</f>
-        <v>45912</v>
+        <v>45933</v>
       </c>
       <c r="Z2" s="17" t="s">
         <v>71</v>
@@ -1339,9 +1338,9 @@
         <v>97</v>
       </c>
       <c r="B3" s="12">
-        <v>10700247</v>
-      </c>
-      <c r="C3" s="32" t="s">
+        <v>10700452</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>106</v>
       </c>
       <c r="D3" s="13" t="s">
@@ -1370,7 +1369,7 @@
       </c>
       <c r="L3" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="M3" s="14" t="s">
         <v>65</v>
@@ -1407,11 +1406,11 @@
       </c>
       <c r="X3" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="Y3" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>45912</v>
+        <v>45933</v>
       </c>
       <c r="Z3" s="17" t="s">
         <v>71</v>
